--- a/personal_trainer_forms/012_fitness_equipment_resource_guide--personal_trainer_forms.xlsx
+++ b/personal_trainer_forms/012_fitness_equipment_resource_guide--personal_trainer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,7 +694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Available space dimensions</t>
+          <t>Form Space Dimensions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Type of equipment</t>
+          <t>Form Equip Type 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Recommended equipment</t>
+          <t>Form Equipment Recommended</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1106,12 +1106,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1173,46 +1173,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_space_types_choices</t>
+          <t>form_goal_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_space_types_choices</t>
+          <t>form_goal_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1224,87 +1224,87 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_goal_type_choices</t>
+          <t>form_goal_type_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_goal_type_choices</t>
+          <t>form_goal_type_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_goal_type_choices</t>
+          <t>form_equip_needed_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_goal_type_choices</t>
+          <t>form_equip_needed_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_goal_type_2_choices</t>
+          <t>form_equip_needed_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_goal_type_2_choices</t>
+          <t>form_equip_needed_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1338,7 +1338,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_equip_needed_choices</t>
+          <t>form_equip_type_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_equip_needed_choices</t>
+          <t>form_equip_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1372,151 +1372,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_equip_needed_2_choices</t>
+          <t>form_equip_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_equip_needed_2_choices</t>
+          <t>form_equip_type_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_equip_type_choices</t>
+          <t>form_equip_type_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>form_equip_type_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>form_equip_type_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>form_equip_type_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>option4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>form_equip_type_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>option5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>option5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>form_equip_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>form_equip_type_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
